--- a/rules/CORE-000180/negative/01/data/unit-test-coreid-CG0308-negative.xlsx
+++ b/rules/CORE-000180/negative/01/data/unit-test-coreid-CG0308-negative.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="dmx.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ae1.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dmx.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae1.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,6 +529,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>Adverse Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Concomitant Medications</t>
         </is>
       </c>
     </row>
@@ -542,38 +555,128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Error group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Error level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Row num</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dmx.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DMX</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ae1.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1622,4 +1725,185 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CMSEQ</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CMTRT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Reported Name of Drug, Med, or Therapy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>123101</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>123101</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IBUPROFEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ABC123</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>123101</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PARACETAMOL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>